--- a/Results/Reports/excels/summary_kg.xlsx
+++ b/Results/Reports/excels/summary_kg.xlsx
@@ -1,77 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\articulos\Spatial_patterns_insects\CODIGOS\Results\Reports\excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D756EF7-C3FA-43EC-BB18-107E0330E8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="3096" yWindow="2916" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="summary_kg" sheetId="1" r:id="rId1"/>
+    <sheet name="summary_kg" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>lables</t>
-  </si>
-  <si>
-    <t>valor</t>
-  </si>
-  <si>
-    <t>Alpha_Percentage</t>
-  </si>
-  <si>
-    <t>Endemism_Percentage</t>
-  </si>
-  <si>
-    <t>Alpha_endemism_Percentage</t>
-  </si>
-  <si>
-    <t>very low</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>moderate</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>very high</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t xml:space="preserve">lables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha_Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endemism_Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha_endemism_Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moderate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -107,15 +100,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -397,11 +381,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -418,93 +402,93 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>72</v>
       </c>
-      <c r="D4">
-        <v>54</v>
-      </c>
-      <c r="E4">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" t="n">
+        <v>52</v>
+      </c>
+      <c r="E4" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>17</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>1</v>
+      <c r="E6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>